--- a/Quantum_Scope_Status.xlsx
+++ b/Quantum_Scope_Status.xlsx
@@ -17,7 +17,7 @@
     <t>Web Application — Quantum · Scope status</t>
   </si>
   <si>
-    <t>Against "Web Application_Quantum.docx" · generated 2026-09-02</t>
+    <t>Against "Web Application_Quantum.docx" · generated 2026-09-10</t>
   </si>
   <si>
     <t>Total points tracked</t>
@@ -95,9 +95,6 @@
     <t>Salary master</t>
   </si>
   <si>
-    <t>1 / 5</t>
-  </si>
-  <si>
     <t>Advances</t>
   </si>
   <si>
@@ -113,7 +110,7 @@
     <t>Salary payment</t>
   </si>
   <si>
-    <t>4 / 7</t>
+    <t>5 / 7</t>
   </si>
   <si>
     <t>Communication</t>
@@ -461,25 +458,28 @@
     <t>Salary master to cover all types of salaries which needs to be given to drivers</t>
   </si>
   <si>
-    <t>Salary Master; server/src/routes/salary-master.js</t>
-  </si>
-  <si>
-    <t>Built this round. A structure is a set of components — earnings and deductions, each a fixed amount or a percentage of basic or gross, each either prorated by attendance or paid whole. A live preview shows what any number of payable days pays. Seeded with realistic placeholders; awaiting the client's actual figures.</t>
+    <t>Salary Master; server/src/payroll/</t>
+  </si>
+  <si>
+    <t>Holds the two structures from the client's own pay registers (July 2026) with the rules they apply: earned components rounded to the rupee, PF 12% on earned basic capped at a 15,000 wage, PT only above 12,000 gross, attendance bonus only at 30+ days, LSA set per driver, employer PF as a company cost. The engine reproduces every one of the 230 drivers in that register to the paisa (npm run test:payroll).</t>
   </si>
   <si>
     <t>HZL Drivers</t>
   </si>
   <si>
-    <t>Salary Master → HZL-STD</t>
-  </si>
-  <si>
-    <t>Structure exists and is linked to deployments. Figures are placeholders.</t>
+    <t>Salary Master → HZL-LNG</t>
+  </si>
+  <si>
+    <t>Fixed 21,050 (Basic+VDA 15,000 · HRA 4,500 · Mobile 300 · Food 1,250), prorated by payable days, no statutory deductions; billed a 2,000 service charge per person on days present plus 18% IGST.</t>
   </si>
   <si>
     <t>Market Drivers</t>
   </si>
   <si>
-    <t>Salary Master → MKT-STD</t>
+    <t>Salary Master → SURAT-LNG</t>
+  </si>
+  <si>
+    <t>The Surat LNG register: Basic+DA 21,750 · HRA 6,525 · Personal 5,225 · Mobile 300 · Halt 1,500 · attendance bonus 3,000 at 30+ days · LSA per driver; PF, PT and employer PF; billed a 2,250 service charge, 18% GST, 2% TDS.</t>
   </si>
   <si>
     <t>Once driver is deployed, it is linked to a salary structure</t>
@@ -494,10 +494,10 @@
     <t>Wage register should be output from system at the end of month once attendance is finalized</t>
   </si>
   <si>
-    <t>Salary → Wage register</t>
-  </si>
-  <si>
-    <t>Computed component by component off the linked structure, with the salary category, the structure code and the statutory deduction as columns. The exact column layout is "as per client requirements" and is still to be supplied.</t>
+    <t>Salary → Pay register (client format)</t>
+  </si>
+  <si>
+    <t>Produced in the client's own layouts, column for column: an HZL DRIVER sheet with the Fixed Gross and Payable salary blocks and the service charge, IGST and invoice footer; a SURAT DRIVER sheet with every component as a fixed/earned pair, PF, CTC and per-driver invoice and TDS. Net payable is worked out from each driver's attendance; totals are live formulas.</t>
   </si>
   <si>
     <t>Supervisor raises the advance request on behalf of the driver</t>
@@ -668,7 +668,7 @@
     <t>Update the details and download the wage register for invoicing purpose</t>
   </si>
   <si>
-    <t>Working; the client's required column layout is still awaited.</t>
+    <t>The pay register carries the service charge, GST, invoice and TDS figures the client is billed on.</t>
   </si>
   <si>
     <t>Download the driver salary payment sheet with option to either hold or pay the driver and edit the attendance</t>
@@ -1268,7 +1268,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>5</v>
@@ -1279,7 +1279,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
@@ -1383,7 +1383,7 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
         <v>28</v>
-      </c>
-      <c r="B18" t="s">
-        <v>29</v>
       </c>
       <c r="C18">
         <v>14</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
         <v>30</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
         <v>32</v>
-      </c>
-      <c r="B20" t="s">
-        <v>33</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
         <v>36</v>
-      </c>
-      <c r="B23" t="s">
-        <v>37</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" t="s">
         <v>38</v>
-      </c>
-      <c r="B24" t="s">
-        <v>39</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -1468,28 +1468,28 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
     </row>
     <row r="27" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
     </row>
     <row r="28" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
     </row>
     <row r="29" ht="46" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1522,7 +1522,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -1532,22 +1532,22 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1558,16 +1558,16 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1578,16 +1578,16 @@
         <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1598,16 +1598,16 @@
         <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1618,16 +1618,16 @@
         <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1638,16 +1638,16 @@
         <v>16</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1658,16 +1658,16 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1678,16 +1678,16 @@
         <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1698,16 +1698,16 @@
         <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1718,16 +1718,16 @@
         <v>16</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1738,16 +1738,16 @@
         <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1758,16 +1758,16 @@
         <v>16</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1778,16 +1778,16 @@
         <v>16</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1798,16 +1798,16 @@
         <v>16</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1818,16 +1818,16 @@
         <v>16</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1838,16 +1838,16 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1858,16 +1858,16 @@
         <v>16</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1878,16 +1878,16 @@
         <v>16</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1898,16 +1898,16 @@
         <v>16</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1918,16 +1918,16 @@
         <v>18</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1938,16 +1938,16 @@
         <v>18</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1958,16 +1958,16 @@
         <v>18</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1978,16 +1978,16 @@
         <v>18</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1998,16 +1998,16 @@
         <v>18</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="4" t="s">
+      <c r="F25" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2018,16 +2018,16 @@
         <v>18</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2038,16 +2038,16 @@
         <v>20</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2058,16 +2058,16 @@
         <v>20</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="F28" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2078,16 +2078,16 @@
         <v>20</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2098,16 +2098,16 @@
         <v>20</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" s="4" t="s">
+      <c r="F30" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2118,16 +2118,16 @@
         <v>20</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="F31" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2138,7 +2138,7 @@
         <v>22</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>4</v>
@@ -2147,7 +2147,7 @@
         <v>22</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2158,7 +2158,7 @@
         <v>22</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>4</v>
@@ -2167,7 +2167,7 @@
         <v>22</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2178,7 +2178,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>4</v>
@@ -2187,7 +2187,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2198,7 +2198,7 @@
         <v>22</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>4</v>
@@ -2207,7 +2207,7 @@
         <v>22</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2218,7 +2218,7 @@
         <v>22</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>4</v>
@@ -2227,7 +2227,7 @@
         <v>22</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2238,7 +2238,7 @@
         <v>22</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>4</v>
@@ -2247,7 +2247,7 @@
         <v>22</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2258,7 +2258,7 @@
         <v>22</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>4</v>
@@ -2267,7 +2267,7 @@
         <v>22</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2278,16 +2278,16 @@
         <v>22</v>
       </c>
       <c r="C39" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D39" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E39" s="4" t="s">
+      <c r="F39" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2298,7 +2298,7 @@
         <v>24</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>4</v>
@@ -2307,7 +2307,7 @@
         <v>24</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2318,7 +2318,7 @@
         <v>24</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>4</v>
@@ -2327,7 +2327,7 @@
         <v>24</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2338,7 +2338,7 @@
         <v>24</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>4</v>
@@ -2347,7 +2347,7 @@
         <v>24</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2358,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>4</v>
@@ -2367,7 +2367,7 @@
         <v>24</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2378,7 +2378,7 @@
         <v>24</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>4</v>
@@ -2387,7 +2387,7 @@
         <v>24</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2398,16 +2398,16 @@
         <v>24</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D45" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="4" t="s">
+      <c r="F45" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2418,16 +2418,16 @@
         <v>24</v>
       </c>
       <c r="C46" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D46" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E46" s="4" t="s">
+      <c r="F46" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2438,16 +2438,16 @@
         <v>26</v>
       </c>
       <c r="C47" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E47" s="4" t="s">
+      <c r="F47" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2458,16 +2458,16 @@
         <v>26</v>
       </c>
       <c r="C48" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E48" s="4" t="s">
+      <c r="F48" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2478,16 +2478,16 @@
         <v>26</v>
       </c>
       <c r="C49" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49" s="4" t="s">
+      <c r="F49" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2520,8 +2520,8 @@
       <c r="C51" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>6</v>
+      <c r="D51" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>160</v>
@@ -2535,7 +2535,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>162</v>
@@ -2555,7 +2555,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>165</v>
@@ -2564,10 +2564,10 @@
         <v>4</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2575,7 +2575,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>166</v>
@@ -2584,10 +2584,10 @@
         <v>4</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2595,7 +2595,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>167</v>
@@ -2604,10 +2604,10 @@
         <v>4</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2615,7 +2615,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>168</v>
@@ -2624,10 +2624,10 @@
         <v>4</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2635,7 +2635,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>169</v>
@@ -2655,7 +2655,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>172</v>
@@ -2675,7 +2675,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>174</v>
@@ -2695,7 +2695,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>177</v>
@@ -2715,7 +2715,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>180</v>
@@ -2735,7 +2735,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>182</v>
@@ -2755,7 +2755,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>185</v>
@@ -2775,7 +2775,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>187</v>
@@ -2795,7 +2795,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>190</v>
@@ -2815,7 +2815,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>193</v>
@@ -2835,7 +2835,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>196</v>
@@ -2847,7 +2847,7 @@
         <v>197</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2855,7 +2855,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>198</v>
@@ -2864,7 +2864,7 @@
         <v>4</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>199</v>
@@ -2875,7 +2875,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>200</v>
@@ -2884,10 +2884,10 @@
         <v>4</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2895,7 +2895,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>201</v>
@@ -2904,10 +2904,10 @@
         <v>4</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2915,7 +2915,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>202</v>
@@ -2924,10 +2924,10 @@
         <v>4</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2935,7 +2935,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>203</v>
@@ -2955,7 +2955,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>206</v>
@@ -2975,7 +2975,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>208</v>
@@ -2995,7 +2995,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>211</v>
@@ -3015,7 +3015,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>214</v>
@@ -3035,13 +3035,13 @@
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D77" s="9" t="s">
-        <v>6</v>
+      <c r="D77" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>160</v>
@@ -3055,7 +3055,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>219</v>
@@ -3075,7 +3075,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>222</v>
@@ -3095,7 +3095,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>224</v>
@@ -3115,7 +3115,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>227</v>
@@ -3135,7 +3135,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>230</v>
@@ -3147,7 +3147,7 @@
         <v>231</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3155,7 +3155,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>232</v>
@@ -3175,7 +3175,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>235</v>
@@ -3195,7 +3195,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>238</v>
@@ -3215,7 +3215,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>241</v>
@@ -3235,7 +3235,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>243</v>
@@ -3255,7 +3255,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>245</v>
@@ -3275,7 +3275,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>248</v>
@@ -3295,7 +3295,7 @@
         <v>88</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>251</v>
